--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -63,7 +63,36 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -76,11 +105,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -92,15 +129,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -116,28 +170,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -151,32 +184,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -190,17 +199,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,187 +215,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,6 +406,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -428,22 +452,16 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -480,24 +498,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -792,7 +792,7 @@
             <v>6</v>
           </cell>
           <cell r="B7" t="str">
-            <v>ネームレス</v>
+            <v>ゴーストアーマー</v>
           </cell>
         </row>
         <row r="8">
@@ -840,7 +840,7 @@
             <v>12</v>
           </cell>
           <cell r="B13" t="str">
-            <v>クリーパー</v>
+            <v>ネームレス</v>
           </cell>
         </row>
         <row r="14">
@@ -856,7 +856,7 @@
             <v>14</v>
           </cell>
           <cell r="B15" t="str">
-            <v>ゴーストアーマー</v>
+            <v>クリーパー</v>
           </cell>
         </row>
         <row r="16">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="D3" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C3,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>クリーパー</v>
       </c>
       <c r="E3">
         <v>40</v>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="D19" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C19,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>クリーパー</v>
       </c>
       <c r="E19">
         <v>15</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="D23" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C23,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ネームレス</v>
       </c>
       <c r="E23">
         <v>15</v>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="D25" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C25,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ネームレス</v>
       </c>
       <c r="E25">
         <v>15</v>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="D26" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C26,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>クリーパー</v>
       </c>
       <c r="E26">
         <v>15</v>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="D28" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C28,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ネームレス</v>
       </c>
       <c r="E28">
         <v>15</v>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="D29" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C29,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>クリーパー</v>
       </c>
       <c r="E29">
         <v>15</v>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D42" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C42,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E42">
         <v>20</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -50,8 +50,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -62,25 +62,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -92,14 +86,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -107,17 +94,9 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -137,24 +116,76 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -168,43 +199,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -215,19 +215,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -239,25 +365,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -269,133 +383,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,6 +406,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -429,30 +444,6 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -481,6 +472,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -495,17 +506,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1737,7 +1737,7 @@
         <v>オーガ</v>
       </c>
       <c r="E14">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F14">
         <v>1</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -62,11 +62,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -78,30 +85,8 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -111,6 +96,21 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -133,13 +133,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -153,9 +146,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -169,33 +176,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -215,19 +215,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -239,163 +245,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,21 +406,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -435,15 +420,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -481,17 +457,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -506,6 +471,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,7 +514,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -523,16 +523,16 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -541,118 +541,118 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1703,11 +1703,11 @@
         <v>2010</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C13,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>ビー</v>
       </c>
       <c r="E13">
         <v>10</v>
@@ -1757,11 +1757,11 @@
         <v>2010</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D15" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C15,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>サーチャー</v>
       </c>
       <c r="E15">
         <v>10</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -63,7 +63,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -74,30 +89,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -116,16 +107,53 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -139,53 +167,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -200,7 +184,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,13 +215,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -233,73 +365,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -311,25 +383,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -342,60 +396,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,6 +406,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -420,39 +429,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -489,6 +465,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -506,6 +491,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,7 +514,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -523,136 +523,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -880,7 +880,7 @@
             <v>101</v>
           </cell>
           <cell r="B18" t="str">
-            <v>アモン</v>
+            <v>アンドラス</v>
           </cell>
         </row>
         <row r="19">
@@ -904,7 +904,7 @@
             <v>104</v>
           </cell>
           <cell r="B21" t="str">
-            <v>アンドラス</v>
+            <v>アモン</v>
           </cell>
         </row>
         <row r="22">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="D30" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C30,[1]TextData!A:A))</f>
-        <v>アンドラス</v>
+        <v>アモン</v>
       </c>
       <c r="E30">
         <v>22</v>
@@ -2351,11 +2351,11 @@
         <v>20010</v>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D37" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C37,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E37">
         <v>15</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D38" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C38,[1]TextData!A:A))</f>
-        <v>アモン</v>
+        <v>アンドラス</v>
       </c>
       <c r="E38">
         <v>15</v>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -48,10 +48,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -63,9 +63,46 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -77,8 +114,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -101,28 +146,38 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -137,23 +192,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -161,46 +200,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -215,19 +215,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -239,163 +377,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -412,8 +412,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -433,16 +433,34 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -465,15 +483,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -483,25 +492,16 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -49,9 +49,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -62,8 +62,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -76,6 +84,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -83,47 +100,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -144,19 +123,47 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -168,10 +175,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -189,22 +205,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -215,67 +215,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -287,115 +395,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,9 +435,41 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -466,43 +498,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1364,7 +1364,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9.54545454545454"/>
@@ -1865,20 +1865,20 @@
         <v>3010</v>
       </c>
       <c r="C19">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="D19" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C19,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ベリト</v>
       </c>
       <c r="E19">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -1892,20 +1892,20 @@
         <v>3010</v>
       </c>
       <c r="C20">
-        <v>102</v>
+        <v>12</v>
       </c>
       <c r="D20" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C20,[1]TextData!A:A))</f>
-        <v>ベリト</v>
+        <v>ネームレス</v>
       </c>
       <c r="E20">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -1913,26 +1913,26 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B21">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D21" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C21,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ネームレス</v>
       </c>
       <c r="E21">
         <v>15</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -1940,26 +1940,26 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B22">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="C22">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D22" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C22,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>ネームレス</v>
       </c>
       <c r="E22">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -1973,20 +1973,20 @@
         <v>3020</v>
       </c>
       <c r="C23">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D23" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C23,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E23">
         <v>15</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1994,26 +1994,26 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="B24">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D24" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C24,[1]TextData!A:A))</f>
-        <v>カースド</v>
+        <v>ソード</v>
       </c>
       <c r="E24">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="B25">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="C25">
         <v>12</v>
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -2048,17 +2048,17 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="B26">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="C26">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D26" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C26,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ネームレス</v>
       </c>
       <c r="E26">
         <v>15</v>
@@ -2067,7 +2067,7 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -2075,17 +2075,17 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="B27">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="C27">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D27" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C27,[1]TextData!A:A))</f>
-        <v>ソード</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E27">
         <v>15</v>
@@ -2102,17 +2102,17 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="B28">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="C28">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D28" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C28,[1]TextData!A:A))</f>
-        <v>ネームレス</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E28">
         <v>15</v>
@@ -2129,17 +2129,17 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="B29">
-        <v>3040</v>
+        <v>3030</v>
       </c>
       <c r="C29">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D29" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C29,[1]TextData!A:A))</f>
-        <v>クリーパー</v>
+        <v>ドライアド</v>
       </c>
       <c r="E29">
         <v>15</v>
@@ -2148,7 +2148,7 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -2156,26 +2156,26 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30">
-        <v>4010</v>
+        <v>3030</v>
       </c>
       <c r="B30">
-        <v>4010</v>
+        <v>3030</v>
       </c>
       <c r="C30">
-        <v>104</v>
+        <v>14</v>
       </c>
       <c r="D30" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C30,[1]TextData!A:A))</f>
-        <v>アモン</v>
+        <v>クリーパー</v>
       </c>
       <c r="E30">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -2183,23 +2183,23 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31">
-        <v>5010</v>
+        <v>3040</v>
       </c>
       <c r="B31">
-        <v>5010</v>
+        <v>3040</v>
       </c>
       <c r="C31">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D31" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C31,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>カースド</v>
       </c>
       <c r="E31">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -2210,23 +2210,23 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32">
-        <v>5010</v>
+        <v>3040</v>
       </c>
       <c r="B32">
-        <v>5010</v>
+        <v>3040</v>
       </c>
       <c r="C32">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="D32" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C32,[1]TextData!A:A))</f>
-        <v>ビフロンス</v>
+        <v>カースド</v>
       </c>
       <c r="E32">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2237,23 +2237,23 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33">
-        <v>5010</v>
+        <v>3040</v>
       </c>
       <c r="B33">
-        <v>5010</v>
+        <v>3040</v>
       </c>
       <c r="C33">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D33" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C33,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>カースド</v>
       </c>
       <c r="E33">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33">
         <v>2</v>
@@ -2264,26 +2264,26 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34">
-        <v>6010</v>
+        <v>3040</v>
       </c>
       <c r="B34">
-        <v>6010</v>
+        <v>3040</v>
       </c>
       <c r="C34">
-        <v>201</v>
+        <v>14</v>
       </c>
       <c r="D34" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C34,[1]TextData!A:A))</f>
-        <v>ファフニール</v>
+        <v>クリーパー</v>
       </c>
       <c r="E34">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -2291,23 +2291,23 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35">
-        <v>20010</v>
+        <v>3050</v>
       </c>
       <c r="B35">
-        <v>20010</v>
+        <v>3050</v>
       </c>
       <c r="C35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D35" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C35,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>カースド</v>
       </c>
       <c r="E35">
         <v>15</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -2318,17 +2318,17 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36">
-        <v>20010</v>
+        <v>3050</v>
       </c>
       <c r="B36">
-        <v>20010</v>
+        <v>3050</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C36,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>カースド</v>
       </c>
       <c r="E36">
         <v>15</v>
@@ -2345,17 +2345,17 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37">
-        <v>20010</v>
+        <v>3050</v>
       </c>
       <c r="B37">
-        <v>20010</v>
+        <v>3050</v>
       </c>
       <c r="C37">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D37" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C37,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>クリーパー</v>
       </c>
       <c r="E37">
         <v>15</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -2372,23 +2372,23 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38">
-        <v>20010</v>
+        <v>3050</v>
       </c>
       <c r="B38">
-        <v>20010</v>
+        <v>3050</v>
       </c>
       <c r="C38">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="D38" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C38,[1]TextData!A:A))</f>
-        <v>アンドラス</v>
+        <v>クリーパー</v>
       </c>
       <c r="E38">
         <v>15</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38">
         <v>4</v>
@@ -2399,26 +2399,26 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39">
-        <v>20020</v>
+        <v>4010</v>
       </c>
       <c r="B39">
-        <v>20020</v>
+        <v>4010</v>
       </c>
       <c r="C39">
-        <v>13</v>
+        <v>104</v>
       </c>
       <c r="D39" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C39,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>アモン</v>
       </c>
       <c r="E39">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -2426,23 +2426,23 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
-        <v>20020</v>
+        <v>5010</v>
       </c>
       <c r="B40">
-        <v>20020</v>
+        <v>5010</v>
       </c>
       <c r="C40">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D40" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C40,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>シールド</v>
       </c>
       <c r="E40">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -2453,20 +2453,20 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41">
-        <v>20020</v>
+        <v>5010</v>
       </c>
       <c r="B41">
-        <v>20020</v>
+        <v>5010</v>
       </c>
       <c r="C41">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D41" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C41,[1]TextData!A:A))</f>
-        <v>パイモン</v>
+        <v>ビフロンス</v>
       </c>
       <c r="E41">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F41">
         <v>1</v>
@@ -2480,28 +2480,271 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42">
-        <v>20020</v>
+        <v>5010</v>
       </c>
       <c r="B42">
-        <v>20020</v>
+        <v>5010</v>
       </c>
       <c r="C42">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D42" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C42,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>シールド</v>
       </c>
       <c r="E42">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42">
         <v>2</v>
       </c>
       <c r="H42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43">
+        <v>6010</v>
+      </c>
+      <c r="B43">
+        <v>6010</v>
+      </c>
+      <c r="C43">
+        <v>201</v>
+      </c>
+      <c r="D43" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C43,[1]TextData!A:A))</f>
+        <v>ファフニール</v>
+      </c>
+      <c r="E43">
+        <v>25</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44">
+        <v>20010</v>
+      </c>
+      <c r="B44">
+        <v>20010</v>
+      </c>
+      <c r="C44">
+        <v>4</v>
+      </c>
+      <c r="D44" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C44,[1]TextData!A:A))</f>
+        <v>ウルフ</v>
+      </c>
+      <c r="E44">
+        <v>15</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45">
+        <v>20010</v>
+      </c>
+      <c r="B45">
+        <v>20010</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C45,[1]TextData!A:A))</f>
+        <v>ネレイドジェム</v>
+      </c>
+      <c r="E45">
+        <v>15</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46">
+        <v>20010</v>
+      </c>
+      <c r="B46">
+        <v>20010</v>
+      </c>
+      <c r="C46">
+        <v>10</v>
+      </c>
+      <c r="D46" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C46,[1]TextData!A:A))</f>
+        <v>スコーピオン</v>
+      </c>
+      <c r="E46">
+        <v>15</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>2</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47">
+        <v>20010</v>
+      </c>
+      <c r="B47">
+        <v>20010</v>
+      </c>
+      <c r="C47">
+        <v>101</v>
+      </c>
+      <c r="D47" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C47,[1]TextData!A:A))</f>
+        <v>アンドラス</v>
+      </c>
+      <c r="E47">
+        <v>15</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>4</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48">
+        <v>20020</v>
+      </c>
+      <c r="B48">
+        <v>20020</v>
+      </c>
+      <c r="C48">
+        <v>13</v>
+      </c>
+      <c r="D48" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C48,[1]TextData!A:A))</f>
+        <v>インプ</v>
+      </c>
+      <c r="E48">
+        <v>12</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>4</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49">
+        <v>20020</v>
+      </c>
+      <c r="B49">
+        <v>20020</v>
+      </c>
+      <c r="C49">
+        <v>13</v>
+      </c>
+      <c r="D49" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C49,[1]TextData!A:A))</f>
+        <v>インプ</v>
+      </c>
+      <c r="E49">
+        <v>20</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50">
+        <v>20020</v>
+      </c>
+      <c r="B50">
+        <v>20020</v>
+      </c>
+      <c r="C50">
+        <v>103</v>
+      </c>
+      <c r="D50" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C50,[1]TextData!A:A))</f>
+        <v>パイモン</v>
+      </c>
+      <c r="E50">
+        <v>25</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51">
+        <v>20020</v>
+      </c>
+      <c r="B51">
+        <v>20020</v>
+      </c>
+      <c r="C51">
+        <v>6</v>
+      </c>
+      <c r="D51" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C51,[1]TextData!A:A))</f>
+        <v>ゴーストアーマー</v>
+      </c>
+      <c r="E51">
+        <v>20</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>2</v>
+      </c>
+      <c r="H51">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -49,14 +49,22 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -71,7 +79,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -84,35 +92,25 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -123,23 +121,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -154,46 +138,62 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -221,181 +221,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -412,8 +412,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -433,17 +433,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -455,6 +444,39 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -476,33 +498,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,145 +514,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1364,7 +1364,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="9.54545454545454"/>
@@ -2405,17 +2405,17 @@
         <v>4010</v>
       </c>
       <c r="C39">
-        <v>104</v>
+        <v>6</v>
       </c>
       <c r="D39" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C39,[1]TextData!A:A))</f>
-        <v>アモン</v>
+        <v>ゴーストアーマー</v>
       </c>
       <c r="E39">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -2426,26 +2426,26 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40">
-        <v>5010</v>
+        <v>4010</v>
       </c>
       <c r="B40">
-        <v>5010</v>
+        <v>4010</v>
       </c>
       <c r="C40">
-        <v>8</v>
+        <v>104</v>
       </c>
       <c r="D40" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C40,[1]TextData!A:A))</f>
-        <v>シールド</v>
+        <v>アモン</v>
       </c>
       <c r="E40">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -2453,26 +2453,26 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41">
-        <v>5010</v>
+        <v>4010</v>
       </c>
       <c r="B41">
-        <v>5010</v>
+        <v>4010</v>
       </c>
       <c r="C41">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="D41" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C41,[1]TextData!A:A))</f>
-        <v>ビフロンス</v>
+        <v>シールド</v>
       </c>
       <c r="E41">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -2499,7 +2499,7 @@
         <v>1</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -2507,20 +2507,20 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43">
-        <v>6010</v>
+        <v>5010</v>
       </c>
       <c r="B43">
-        <v>6010</v>
+        <v>5010</v>
       </c>
       <c r="C43">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="D43" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C43,[1]TextData!A:A))</f>
-        <v>ファフニール</v>
+        <v>ビフロンス</v>
       </c>
       <c r="E43">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -2534,26 +2534,26 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44">
-        <v>20010</v>
+        <v>5010</v>
       </c>
       <c r="B44">
-        <v>20010</v>
+        <v>5010</v>
       </c>
       <c r="C44">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D44" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C44,[1]TextData!A:A))</f>
-        <v>ウルフ</v>
+        <v>シールド</v>
       </c>
       <c r="E44">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -2561,23 +2561,23 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45">
-        <v>20010</v>
+        <v>6010</v>
       </c>
       <c r="B45">
-        <v>20010</v>
+        <v>6010</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>201</v>
       </c>
       <c r="D45" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C45,[1]TextData!A:A))</f>
-        <v>ネレイドジェム</v>
+        <v>ファフニール</v>
       </c>
       <c r="E45">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2594,11 +2594,11 @@
         <v>20010</v>
       </c>
       <c r="C46">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D46" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C46,[1]TextData!A:A))</f>
-        <v>スコーピオン</v>
+        <v>ウルフ</v>
       </c>
       <c r="E46">
         <v>15</v>
@@ -2607,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -2621,20 +2621,20 @@
         <v>20010</v>
       </c>
       <c r="C47">
-        <v>101</v>
+        <v>1</v>
       </c>
       <c r="D47" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C47,[1]TextData!A:A))</f>
-        <v>アンドラス</v>
+        <v>ネレイドジェム</v>
       </c>
       <c r="E47">
         <v>15</v>
       </c>
       <c r="F47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -2642,26 +2642,26 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="B48">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="C48">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D48" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C48,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>スコーピオン</v>
       </c>
       <c r="E48">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F48">
         <v>0</v>
       </c>
       <c r="G48">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -2669,26 +2669,26 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="B49">
-        <v>20020</v>
+        <v>20010</v>
       </c>
       <c r="C49">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="D49" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C49,[1]TextData!A:A))</f>
-        <v>インプ</v>
+        <v>アンドラス</v>
       </c>
       <c r="E49">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -2702,20 +2702,20 @@
         <v>20020</v>
       </c>
       <c r="C50">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="D50" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C50,[1]TextData!A:A))</f>
-        <v>パイモン</v>
+        <v>インプ</v>
       </c>
       <c r="E50">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -2729,11 +2729,11 @@
         <v>20020</v>
       </c>
       <c r="C51">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D51" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(C51,[1]TextData!A:A))</f>
-        <v>ゴーストアーマー</v>
+        <v>インプ</v>
       </c>
       <c r="E51">
         <v>20</v>
@@ -2742,9 +2742,63 @@
         <v>0</v>
       </c>
       <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52">
+        <v>20020</v>
+      </c>
+      <c r="B52">
+        <v>20020</v>
+      </c>
+      <c r="C52">
+        <v>103</v>
+      </c>
+      <c r="D52" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C52,[1]TextData!A:A))</f>
+        <v>パイモン</v>
+      </c>
+      <c r="E52">
+        <v>25</v>
+      </c>
+      <c r="F52">
+        <v>1</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53">
+        <v>20020</v>
+      </c>
+      <c r="B53">
+        <v>20020</v>
+      </c>
+      <c r="C53">
+        <v>6</v>
+      </c>
+      <c r="D53" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(C53,[1]TextData!A:A))</f>
+        <v>ゴーストアーマー</v>
+      </c>
+      <c r="E53">
+        <v>20</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
         <v>2</v>
       </c>
-      <c r="H51">
+      <c r="H53">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/Troops.xlsx
+++ b/Assets/Data/Troops.xlsx
@@ -50,29 +50,13 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -93,7 +77,38 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -106,16 +121,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -130,7 +161,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -144,24 +175,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -169,17 +184,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -198,13 +205,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -215,12 +215,114 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -233,37 +335,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -275,13 +383,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -293,109 +395,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,15 +406,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -429,6 +420,24 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -448,24 +457,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -477,6 +468,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,25 +514,25 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -541,118 +541,118 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
